--- a/Jonail Jail/GBPS Jonail Jail Data.xlsx
+++ b/Jonail Jail/GBPS Jonail Jail Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Jonail Jail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D56809-7AE2-488F-A9BB-A1C24053F75E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39FEEB09-2844-49C4-8039-CF287CC8464F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1422,10 +1422,10 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1967,22 +1967,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="10" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
     </row>
     <row r="2" spans="1:14" s="12" customFormat="1" ht="15.75">
       <c r="A2" s="7" t="s">
@@ -6913,18 +6913,18 @@
       </c>
     </row>
     <row r="117" spans="1:14">
-      <c r="E117" s="50"/>
+      <c r="E117" s="49"/>
     </row>
     <row r="121" spans="1:14">
-      <c r="F121" s="50"/>
-      <c r="G121" s="50"/>
+      <c r="F121" s="49"/>
+      <c r="G121" s="49"/>
     </row>
     <row r="123" spans="1:14">
-      <c r="E123" s="50"/>
+      <c r="E123" s="49"/>
     </row>
     <row r="127" spans="1:14">
-      <c r="F127" s="50"/>
-      <c r="G127" s="50"/>
+      <c r="F127" s="49"/>
+      <c r="G127" s="49"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:N113">
